--- a/data/LM4_LMI_Summary.xlsx
+++ b/data/LM4_LMI_Summary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dafha\Work Colleague\Mba rida\Event\MAILER\without raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dafha\Work Colleague\OS\Mba rida\Event\MAILER\new begin_stk\without raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF564B5C-EEB3-46B5-9E54-A7C9E425D2CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C4ACA66-BD7C-41E8-A488-9AF3306E9B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F673BAF6-C00D-42EA-9313-7CB2BD08351B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{F673BAF6-C00D-42EA-9313-7CB2BD08351B}"/>
   </bookViews>
   <sheets>
     <sheet name="By Store" sheetId="4" r:id="rId1"/>
@@ -28,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -418,11 +420,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -480,10 +483,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -546,11 +549,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A330CECB-2FBC-4EEA-97BC-52EEAA24B3EB}"/>
     <cellStyle name="Normal 3" xfId="3" xr:uid="{306D26D0-5A54-4950-898A-EDF3634FF0A7}"/>
+    <cellStyle name="Normal 4" xfId="4" xr:uid="{C9989667-9E99-4005-8FED-1DEBC0B9864F}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1624,28 +1628,28 @@
     <row r="3" spans="1:14">
       <c r="A3" s="42"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="J3" s="22" t="s">
+      <c r="J3" s="21" t="s">
         <v>40</v>
       </c>
       <c r="K3" s="23" t="s">
